--- a/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
+++ b/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kleinschmidtgroup-my.sharepoint.com/personal/kevin_nebiolo_kleinschmidtgroup_com/Documents/Software/stryke/Spreadsheet Interface/Examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF16DB8D-5A91-435A-A361-62934D9C5B17}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC61185-3205-4BB3-BE2C-1B9221D332EC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="816" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="816" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Background and Metadata" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <t>Log Normal</t>
   </si>
   <si>
-    <t>Genus = 'Micropterus', Month = [3,4,5], HUC02= [2]</t>
+    <t>Genus = 'Micropterus', Month = [3,4,5], HUC02= [4]</t>
   </si>
 </sst>
 </file>
@@ -1575,8 +1575,7 @@
     <col min="2" max="2" width="16.42578125" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="53" width="9.140625" style="28" customWidth="1"/>
     <col min="54" max="55" width="9.140625" customWidth="1"/>
   </cols>
@@ -24260,13 +24259,13 @@
         <v>18</v>
       </c>
       <c r="F13">
-        <v>0.9657</v>
+        <v>1.3713</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1.2999999999999999E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="I13" t="s">
         <v>101</v>

--- a/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
+++ b/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kleinschmidtgroup-my.sharepoint.com/personal/kevin_nebiolo_kleinschmidtgroup_com/Documents/Software/stryke/Spreadsheet Interface/Examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC61185-3205-4BB3-BE2C-1B9221D332EC}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D8DDCB-6B82-4C0E-B9F8-1807F77086CE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="816" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="816" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Background and Metadata" sheetId="1" r:id="rId1"/>
@@ -24277,7 +24277,7 @@
         <v>0.4118</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="O13">
         <v>1.6</v>

--- a/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
+++ b/Spreadsheet Interface/Examples/Run_of_River_Simple_Network_Townsend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kleinschmidtgroup-my.sharepoint.com/personal/kevin_nebiolo_kleinschmidtgroup_com/Documents/Software/stryke/Spreadsheet Interface/Examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D8DDCB-6B82-4C0E-B9F8-1807F77086CE}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_27B02BB3AB9659DB438820632D6AFBD2D6A3435B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CDD01B2-B8C4-457F-A8C6-0A00E2591282}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="816" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24277,7 +24277,7 @@
         <v>0.4118</v>
       </c>
       <c r="L13">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>1.6</v>
